--- a/artfynd/A 60688-2023 artfynd.xlsx
+++ b/artfynd/A 60688-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60688-2023 artfynd.xlsx
+++ b/artfynd/A 60688-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66538699</v>
+        <v>68501512</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svenskmyrarna, Vrm</t>
+          <t>Svenskmyrarna, söder om, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344223.6017064041</v>
+        <v>344325</v>
       </c>
       <c r="R2" t="n">
-        <v>6604342.545750719</v>
+        <v>6604303</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +746,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera bålar på gammal tall. Rio Göteborg NoK.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,39 +768,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>21484</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68501512</v>
+        <v>116484043</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -826,25 +812,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svenskmyrarna, söder om, Vrm</t>
+          <t>Lilla Sävtjärnen, Lilla Sävtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344325.1711780716</v>
+        <v>344073</v>
       </c>
       <c r="R3" t="n">
-        <v>6604302.801480542</v>
+        <v>6604319</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,27 +848,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera bålar på gammal tall. Rio Göteborg NoK.</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +878,117 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>66538699</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svenskmyrarna, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>344224</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6604343</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>21484</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
